--- a/ex2-kmeans/Results/Tiempos_3_clusters.xlsx
+++ b/ex2-kmeans/Results/Tiempos_3_clusters.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Estudio\OneDrive - Universidad de Antioquia\Estudio\Materias\S9\Arquitectura Avanzada\Labs\Lab2-GPU\ex2-kmeans\Results\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{ADD79F26-483E-4D46-8241-B129E3EB0E9D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F020605B-ABA0-4E29-8ED1-5188C358BC7C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{10211266-07E5-4C49-AC3C-F041C1635583}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="23">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="26">
   <si>
     <t>GPU_TOTAL</t>
   </si>
@@ -50,61 +50,70 @@
     <t>CPU_AVG</t>
   </si>
   <si>
-    <t>1K</t>
-  </si>
-  <si>
-    <t>10K</t>
-  </si>
-  <si>
-    <t>100K</t>
-  </si>
-  <si>
-    <t>1000K</t>
-  </si>
-  <si>
-    <t>0.169</t>
-  </si>
-  <si>
-    <t>0.056</t>
-  </si>
-  <si>
-    <t>0.154</t>
-  </si>
-  <si>
-    <t>0.077</t>
-  </si>
-  <si>
-    <t>0.791</t>
-  </si>
-  <si>
-    <t>0.018</t>
-  </si>
-  <si>
-    <t>0.969</t>
-  </si>
-  <si>
-    <t>0.019</t>
-  </si>
-  <si>
-    <t>2145.4</t>
-  </si>
-  <si>
-    <t>42.91</t>
-  </si>
-  <si>
-    <t>187.4</t>
-  </si>
-  <si>
-    <t>4.3</t>
-  </si>
-  <si>
-    <t>0.991</t>
-  </si>
-  <si>
-    <t>0.495</t>
-  </si>
-  <si>
-    <t>0.167</t>
+    <t>100k</t>
+  </si>
+  <si>
+    <t>1M</t>
+  </si>
+  <si>
+    <t>10M</t>
+  </si>
+  <si>
+    <t>GPU Basica</t>
+  </si>
+  <si>
+    <t>0.3</t>
+  </si>
+  <si>
+    <t>3.4</t>
+  </si>
+  <si>
+    <t>891.4</t>
+  </si>
+  <si>
+    <t>0.4</t>
+  </si>
+  <si>
+    <t>1200.7</t>
+  </si>
+  <si>
+    <t>46.4</t>
+  </si>
+  <si>
+    <t>GPU OPT</t>
+  </si>
+  <si>
+    <t>3.1</t>
+  </si>
+  <si>
+    <t>0.07</t>
+  </si>
+  <si>
+    <t>CPU</t>
+  </si>
+  <si>
+    <t>234.4</t>
+  </si>
+  <si>
+    <t>4.5</t>
+  </si>
+  <si>
+    <t>176.4</t>
+  </si>
+  <si>
+    <t>24.17</t>
+  </si>
+  <si>
+    <t>0.46</t>
+  </si>
+  <si>
+    <t>126.23</t>
+  </si>
+  <si>
+    <t>4.8</t>
+  </si>
+  <si>
+    <t>Iteraciones</t>
   </si>
 </sst>
 </file>
@@ -140,8 +149,14 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -476,92 +491,130 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{40BCD430-ACAB-4E21-90A2-195B9CF028FF}">
-  <dimension ref="A1:E5"/>
+  <dimension ref="A1:H5"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="B1" t="s">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="B1" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="C1" s="2"/>
+      <c r="D1" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="E1" s="2"/>
+      <c r="F1" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="G1" s="2"/>
+      <c r="H1" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="B2" t="s">
+        <v>2</v>
+      </c>
+      <c r="C2" t="s">
+        <v>3</v>
+      </c>
+      <c r="D2" t="s">
         <v>0</v>
       </c>
-      <c r="C1" t="s">
+      <c r="E2" t="s">
         <v>1</v>
       </c>
-      <c r="D1" t="s">
-        <v>2</v>
-      </c>
-      <c r="E1" t="s">
-        <v>3</v>
+      <c r="F2" t="s">
+        <v>0</v>
+      </c>
+      <c r="G2" t="s">
+        <v>1</v>
+      </c>
+      <c r="H2">
+        <v>42</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
+    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
         <v>4</v>
       </c>
-      <c r="B2" t="s">
+      <c r="B3" s="1">
+        <v>19</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="D3" s="1">
+        <v>14</v>
+      </c>
+      <c r="E3" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="C2" t="s">
+      <c r="F3" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="G3" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="H3">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>5</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="E4" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="D2" t="s">
+      <c r="F4" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="G4" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="E2" t="s">
-        <v>9</v>
+      <c r="H4">
+        <v>27</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
-        <v>5</v>
-      </c>
-      <c r="B3" t="s">
+    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>6</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="D5" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="C3" t="s">
-        <v>11</v>
-      </c>
-      <c r="D3" t="s">
-        <v>20</v>
-      </c>
-      <c r="E3" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
-        <v>6</v>
-      </c>
-      <c r="B4" t="s">
-        <v>12</v>
-      </c>
-      <c r="C4" t="s">
-        <v>13</v>
-      </c>
-      <c r="D4" t="s">
-        <v>18</v>
-      </c>
-      <c r="E4" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
-        <v>7</v>
-      </c>
-      <c r="B5" t="s">
-        <v>14</v>
-      </c>
-      <c r="C5" t="s">
-        <v>15</v>
-      </c>
-      <c r="D5" t="s">
-        <v>16</v>
-      </c>
-      <c r="E5" t="s">
-        <v>17</v>
+      <c r="E5" s="1">
+        <v>33</v>
+      </c>
+      <c r="F5" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="G5" s="1" t="s">
+        <v>24</v>
       </c>
     </row>
   </sheetData>
+  <mergeCells count="3">
+    <mergeCell ref="D1:E1"/>
+    <mergeCell ref="F1:G1"/>
+    <mergeCell ref="B1:C1"/>
+  </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>